--- a/docs/samples/products-template.xlsx
+++ b/docs/samples/products-template.xlsx
@@ -49,13 +49,13 @@
     <t>images</t>
   </si>
   <si>
-    <t>DK-TSHIRT-001</t>
-  </si>
-  <si>
-    <t>DKKart Cotton Polo T-Shirt (Navy)</t>
-  </si>
-  <si>
-    <t>DKKart</t>
+    <t>DG-TSHIRT-001</t>
+  </si>
+  <si>
+    <t>DGkart Cotton Polo T-Shirt (Navy)</t>
+  </si>
+  <si>
+    <t>DGkart</t>
   </si>
   <si>
     <t>Men's Clothing</t>
@@ -73,10 +73,10 @@
     <t>Colour=Navy; Size=M; Fabric=Cotton</t>
   </si>
   <si>
-    <t>dk-tshirt-001_1.jpg, dk-tshirt-001_2.jpg</t>
-  </si>
-  <si>
-    <t>DK-EARBUD-002</t>
+    <t>dg-tshirt-001_1.jpg, dg-tshirt-001_2.jpg</t>
+  </si>
+  <si>
+    <t>DG-EARBUD-002</t>
   </si>
   <si>
     <t>Wireless Earbuds with ANC</t>
